--- a/output/parameter_dictionary.xlsx
+++ b/output/parameter_dictionary.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-17T01:34:09+00:00 · methodology v2.0.0 · regenerate with: python make_parameter_dictionary.py</t>
+          <t>Generated 2026-07-19T16:01:46+00:00 · methodology v2.0.0 · regenerate with: python make_parameter_dictionary.py</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2757,39 +2757,39 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Anchor size factor</t>
+          <t>Positioning shrinkage (non-market bases)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>rev &lt; ₹100 Cr → ×0.8 · rev &lt; ₹500 Cr → ×0.9 · else ×1.00</t>
+          <t>λ = 0.5</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>core/calibration.py</t>
+          <t>core/pipeline.py _POSITION_SHRINK_NONMARKET</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>haircuts the sector anchor for small targets</t>
+          <t>on book/sector-calibrated bases the margin position moves only halfway from the median toward the margin rank</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>published aggregates skew large-cap; small-caps trade at a discount</t>
+          <t>the margin→multiple link is verified only on market data; Jul-2026 real-market spot checks showed full-strength positioning can point the wrong way on calibrated bases</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EV/EBIT anchor uplift</t>
+          <t>Anchor size factor</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA anchor × 1.25</t>
+          <t>rev &lt; ₹100 Cr → ×0.9 · rev &lt; ₹500 Cr → ×0.95 · else ×1.00</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2799,51 +2799,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D&amp;A ≈ 20% of EBITDA for Indian industrials</t>
+          <t>haircuts the sector anchor for small targets</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>keeps the three methods internally consistent</t>
+          <t>published aggregates skew large-cap; small-caps trade at a discount</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — AUTO</t>
+          <t>EV/EBIT anchor uplift</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 11.0x · EV/Sales 1.4x</t>
+          <t>EV/EBITDA anchor × 1.25</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>core/calibration.py SECTOR_ANCHORS</t>
+          <t>core/calibration.py</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>re-levels book multiples when &lt; 3 listed comps exist</t>
+          <t>D&amp;A ≈ 20% of EBITDA for Indian industrials</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>India sector aggregates (Damodaran, Jan-2025) — editable calibration defaults; replace with a live market feed for exact levels</t>
+          <t>keeps the three methods internally consistent</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — BUILDMAT</t>
+          <t>Sector anchor — AUTO</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 11.0x · EV/Sales 1.6x</t>
+          <t>EV/EBITDA 14.0x · EV/Sales 1.8x</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — CHEM</t>
+          <t>Sector anchor — BUILDMAT</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 12.0x · EV/Sales 2.0x</t>
+          <t>EV/EBITDA 14.0x · EV/Sales 2.0x</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — CONSTR</t>
+          <t>Sector anchor — CHEM</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 9.0x · EV/Sales 1.3x</t>
+          <t>EV/EBITDA 16.0x · EV/Sales 2.6x</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — ELEC</t>
+          <t>Sector anchor — CONSTR</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 13.0x · EV/Sales 1.5x</t>
+          <t>EV/EBITDA 11.0x · EV/Sales 1.6x</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — ENERGY</t>
+          <t>Sector anchor — ELEC</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 7.0x · EV/Sales 1.1x</t>
+          <t>EV/EBITDA 17.0x · EV/Sales 2.0x</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — FOOD</t>
+          <t>Sector anchor — ENERGY</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 12.0x · EV/Sales 1.3x</t>
+          <t>EV/EBITDA 8.5x · EV/Sales 1.3x</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3000,12 +3000,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — HOTEL</t>
+          <t>Sector anchor — FOOD</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 12.0x · EV/Sales 2.5x</t>
+          <t>EV/EBITDA 14.0x · EV/Sales 1.6x</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — IT</t>
+          <t>Sector anchor — HOTEL</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 15.0x · EV/Sales 2.8x</t>
+          <t>EV/EBITDA 15.0x · EV/Sales 3.1x</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — LOGIST</t>
+          <t>Sector anchor — IT</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 10.0x · EV/Sales 1.4x</t>
+          <t>EV/EBITDA 17.0x · EV/Sales 3.2x</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — MACH</t>
+          <t>Sector anchor — LOGIST</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 13.0x · EV/Sales 1.8x</t>
+          <t>EV/EBITDA 12.0x · EV/Sales 1.7x</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — MEDIA</t>
+          <t>Sector anchor — MACH</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 10.0x · EV/Sales 1.8x</t>
+          <t>EV/EBITDA 18.0x · EV/Sales 2.5x</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — METAL</t>
+          <t>Sector anchor — MEDIA</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 7.0x · EV/Sales 1.0x</t>
+          <t>EV/EBITDA 11.0x · EV/Sales 2.0x</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — MINING</t>
+          <t>Sector anchor — METAL</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 6.5x · EV/Sales 1.4x</t>
+          <t>EV/EBITDA 9.0x · EV/Sales 1.3x</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — PHARMA</t>
+          <t>Sector anchor — MINING</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 14.0x · EV/Sales 3.0x</t>
+          <t>EV/EBITDA 9.0x · EV/Sales 1.9x</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — POLYPAPER</t>
+          <t>Sector anchor — PHARMA</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 8.5x · EV/Sales 1.0x</t>
+          <t>EV/EBITDA 17.0x · EV/Sales 3.6x</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — RETAIL</t>
+          <t>Sector anchor — POLYPAPER</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 14.0x · EV/Sales 1.2x</t>
+          <t>EV/EBITDA 10.0x · EV/Sales 1.2x</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — SERVICES</t>
+          <t>Sector anchor — RETAIL</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 12.0x · EV/Sales 1.8x</t>
+          <t>EV/EBITDA 17.0x · EV/Sales 1.5x</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Sector anchor — TEXTILE</t>
+          <t>Sector anchor — SERVICES</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>EV/EBITDA 8.0x · EV/Sales 0.9x</t>
+          <t>EV/EBITDA 14.0x · EV/Sales 2.2x</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3324,25 +3324,52 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>Sector anchor — TEXTILE</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 9.5x · EV/Sales 1.1x</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>core/calibration.py SECTOR_ANCHORS</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>re-levels book multiples when &lt; 3 listed comps exist</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>India sector aggregates (Damodaran, Jan-2025) — editable calibration defaults; replace with a live market feed for exact levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>Sector anchor — TRADE</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 9.0x · EV/Sales 0.5x</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 11.0x · EV/Sales 0.6x</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>core/calibration.py SECTOR_ANCHORS</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>re-levels book multiples when &lt; 3 listed comps exist</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>India sector aggregates (Damodaran, Jan-2025) — editable calibration defaults; replace with a live market feed for exact levels</t>
         </is>
